--- a/m1/a1-ecossistema-e-fisica/exercicio/pedidos-em-producao.xlsx
+++ b/m1/a1-ecossistema-e-fisica/exercicio/pedidos-em-producao.xlsx
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
-  <fonts count="4">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +31,15 @@
     </font>
     <font>
       <i val="1"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -48,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +76,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,31 +442,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GRÁFICA AURORA · Relatório de Ordens de Serviço em Produção</t>
+          <t>GRÁFICA AURORA · Relatório de ordens de serviço</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Emitido em 16/07/2026 às 07:42 · Usuário: PCP01 · Filtro: status &lt;&gt; Cancelado</t>
+          <t>Emitido em 16/07/2026 08:12 · módulo PCP · todas as OS abertas no período</t>
         </is>
       </c>
     </row>
@@ -520,40 +523,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Distribuidora Sertão</t>
+          <t>Rede Sabor Caseiro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rótulo adesivo</t>
+          <t>Caixa cartucho</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Em produção</t>
+          <t>Entregue</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Flexo 1</t>
+          <t>Offset 2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.450,00</t>
+          <t>31.861,33</t>
         </is>
       </c>
     </row>
@@ -563,39 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Laticínios Vale Verde</t>
+          <t>Rede Sabor Caseiro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Caixa cartucho</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3500</v>
+          <t>Etiqueta térmica</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>35.000</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>16-jul-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aguardando papel</t>
+          <t>entregue</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Offset 2</t>
+          <t>Flexo 1</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>12300</v>
+        <v>26800.39</v>
       </c>
     </row>
     <row r="7">
@@ -604,35 +609,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Farmácia Popular Norte</t>
+          <t>Laticínios Vale Verde</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bula</t>
+          <t>Rótulo adesivo</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>46207</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>46214</v>
+        <v>1500</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>07-jul-26</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Em produção</t>
+          <t>entregue</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Offset 1</t>
+          <t>Flexo 2</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6120.5</v>
+        <v>6741.86</v>
       </c>
     </row>
     <row r="8">
@@ -641,193 +650,236 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Distribuidora Sertão</t>
+          <t>Clínica Santa Clara</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rótulo adesivo</t>
+          <t>Bloco de notas</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENTREGUE</t>
+          <t>em produção</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18.592,49</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2422</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cosméticos Flor de Lis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24-jul-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Aguardando aprovação</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Flexo 1</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5980,00</t>
-        </is>
+      <c r="I9" t="n">
+        <v>38903.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Móveis Cariri</t>
+          <t>Distrib. Sertão</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Catálogo 24p</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1200</v>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>05-jul-26</t>
+          <t>10-jul-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Em produção</t>
+          <t>EM PRODUÇÃO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Offset 2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>18.900,00</t>
-        </is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>33081.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Laticínios Vale Verde</t>
+          <t>Supermercados Praia Nova</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rótulo adesivo</t>
+          <t>Caixa cartucho</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15000</v>
+        <v>2500</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aguardando aprovação</t>
+          <t>Em acabamento</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Flexo 2</t>
+          <t>Offset 3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9.750,00</t>
+          <t>6.270,24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supermercado Bom Preço</t>
+          <t>Bebidas Jangada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Encarte 8p</t>
+          <t>Bula</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>46211</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>46217</v>
+        <v>4000</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>19-jul-26</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Em produção</t>
+          <t>ENTREGUE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Offset 1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>22.400,00</t>
-        </is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4955.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Farmácia Popular Norte</t>
+          <t>Laticínios Vale Verde</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Caixa cartucho</t>
+          <t>Rótulo adesivo</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>12-jul-26</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -837,65 +889,65 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Offset 2</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7.850,00</t>
-        </is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>24860.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Óticas Miranda</t>
+          <t>Editora Céu Azul</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sacola personalizada</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>5000</v>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Em produção</t>
+          <t>em produção</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Flexo 2</t>
+          <t>Offset 3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11.200,00</t>
+          <t>10.910,92</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Distribuidora Sertão</t>
+          <t>Bebidas Jangada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -904,141 +956,143 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>46212</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>46216</v>
+        <v>6000</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>22-jul-26</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Em produção</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Offset 1</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>16.800,00</t>
-        </is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>24238.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Móveis Cariri</t>
+          <t>Rede Sabor Caseiro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rótulo adesivo</t>
+          <t>Bloco de notas</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>16-jul-26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Em produção</t>
+          <t>Entregue</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Flexo 1</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4.300,00</t>
-        </is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>18804.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supermercado Bom Preço</t>
+          <t>Editora Céu Azul</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Caixa cartucho</t>
+          <t>Embalagem flexível</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9000</v>
+        <v>35000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10-jul-26</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aguardando aprovação</t>
+          <t>EM PRODUÇÃO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Offset 2</t>
+          <t>Flexo 1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.600,00</t>
+          <t>24.013,45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Padaria Central</t>
+          <t>Óticas Miranda</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bula</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>18000</v>
+          <t>Encarte 8p</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>06-jul-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1048,18 +1102,16 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Offset 1</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5.400,00</t>
-        </is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6139.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1068,64 +1120,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Catálogo 24p</t>
+          <t>Sacola personalizada</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>800</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>46215</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>46228</v>
+        <v>30000</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>04-jul-26</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Aguardando papel</t>
+          <t>entregue</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Offset 2</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>14.100,00</t>
-        </is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>9904.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Óticas Miranda</t>
+          <t>Laticínios Vale Verde</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rótulo adesivo</t>
+          <t>Sacola personalizada</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11000</v>
+        <v>1500</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>entregue</t>
+          <t>Entregue</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1135,22 +1189,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.900,00</t>
+          <t>14.632,16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Distribuidora Sertão</t>
+          <t>Confecções Tropical</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sacola personalizada</t>
+          <t>Embalagem flexível</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1158,60 +1212,60 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>12-jul-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Em produção</t>
+          <t>Aguardando aprovação</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Flexo 1</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>9.600,00</t>
-        </is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>36799.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Farmácia Popular Norte</t>
+          <t>Confecções Tropical</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Encarte 8p</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>35000</v>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>07-jul-26</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>em produção</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1219,10 +1273,8 @@
           <t>Offset 1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>19.250,00</t>
-        </is>
+      <c r="I22" t="n">
+        <v>35230.2</v>
       </c>
     </row>
     <row r="23">
@@ -1231,40 +1283,4301 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Confecções Tropical</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>38.372,33</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2436</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Farmácia Bem Estar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Encarte 8p</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>27-jul-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>18860.81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2437</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Distrib. Sertão</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>04-jul-26</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>19527.19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2438</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bula</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12.336,38</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2439</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Confecções Tropical</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Catálogo institucional</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>11-jul-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5487.38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2440</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cosméticos Flor de Lis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cardápio laminado</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>27-jun-26</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Aguardando aprovação</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>23579.97</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2441</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cardápio laminado</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>27.109,30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2442</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Embalagem flexível</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>18.000</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>03-jul-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>31763.54</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2443</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Etiqueta térmica</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10-jul-26</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>29477.97</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2444</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35.874,66</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2445</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>28-jul-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>38344.27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2446</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8.000</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>07-jul-26</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>22214.86</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2447</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aguardando aprovação</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15.894,96</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2448</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>15-jul-26</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>34117.76</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2449</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Distrib. Sertão</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28-jun-26</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>21506.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2450</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Rótulo adesivo</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>50.000</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>27.723,70</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2451</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Confecções Tropical</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>20-jul-26</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>24099.25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2452</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13-jul-26</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>22744.19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2453</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Farmácia Bem Estar</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bula</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>21.902,63</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2454</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rede Sabor Caseiro</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>17-jul-26</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>21517.71</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2455</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>29-jun-26</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Em pré-impressão</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>25196.98</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2456</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Construtora Horizonte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>28.194,75</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2457</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Confecções Tropical</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>02-ago-26</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>EM PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>37683.05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2458</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Catálogo institucional</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>50.000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15-jul-26</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>37814.41</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2459</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Distribuidora Sertão</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10.818,14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2460</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Bebidas Jangada</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>19-jul-26</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>24368.92</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2461</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Óticas Miranda</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>05-jul-26</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>21379.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2462</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Rede Sabor Caseiro</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>29.475,51</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2463</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Confecções Tropical</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Encarte 8p</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>07-jul-26</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Em pré-impressão</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>3148.57</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2464</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Distrib. Sertão</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Catálogo institucional</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>27-jun-26</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>36594.49</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2465</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Bebidas Jangada</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Catálogo institucional</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>17.588,67</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2466</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>22-jul-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>3434.36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2467</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rede Sabor Caseiro</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Embalagem flexível</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>04-jul-26</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>EM PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>4422.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2468</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Óticas Miranda</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>19.949,31</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2469</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Encarte 8p</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>24-jul-26</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>EM PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>23475.75</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2470</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Rede Sabor Caseiro</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>10-jul-26</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>7240.74</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2471</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Etiqueta térmica</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>24.228,71</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2472</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>24-jul-26</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>16967.06</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2473</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Rótulo adesivo</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>14-jul-26</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>31015.43</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2474</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Padaria Central</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>30.000</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>13.619,23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2475</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Etiqueta térmica</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>27-jul-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>14427.36</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2476</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>28-jun-26</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>41315.66</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2477</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cosméticos Flor de Lis</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>Caixa cartucho</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D66" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>33.441,74</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2478</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Embalagem flexível</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>11.000</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>04-jul-26</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>11686.41</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2479</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Catálogo institucional</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>08-jul-26</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>5131.22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2480</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12.943,67</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2481</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10-jul-26</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>25996.04</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2481</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>30.000</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>06-jul-26</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>27992.57</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2482</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Construtora Horizonte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>2500</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>17.560,18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2483</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Rede Sabor Caseiro</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Embalagem flexível</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>12-jul-26</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>37353.69</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2484</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Construtora Horizonte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>28-jun-26</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>16452.43</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2485</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Encarte 8p</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>14.643,09</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2486</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Óticas Miranda</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>17-jul-26</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>9675.459999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2487</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>01-jul-26</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>3964.2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2488</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Em pré-impressão</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>9.373,35</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2489</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Construtora Horizonte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8.000</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>21-jul-26</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>41251.35</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2490</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Cosméticos Flor de Lis</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>27-jun-26</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>10250.63</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2491</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Óticas Miranda</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Calendário de mesa</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>14.734,19</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2492</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cosméticos Flor de Lis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Etiqueta térmica</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>04-jul-26</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>18012.02</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2493</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>35.000</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>07-jul-26</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Aguardando aprovação</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>3249.71</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2494</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Etiqueta térmica</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>21.385,85</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2495</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Padaria Central</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>09-jul-26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>20352.37</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2496</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Padaria Central</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>02-jul-26</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Em pré-impressão</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>18638.92</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2497</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>27.141,36</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2498</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Confecções Tropical</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>18-jul-26</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Aguardando aprovação</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>18463.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2499</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Farmácia Bem Estar</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>16-jul-26</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>24/07/2026</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>8525.120000000001</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5.324,56</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2501</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Cardápio laminado</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>50.000</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>21-jul-26</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>36997.14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2502</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Rede Sabor Caseiro</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bula</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>06-jul-26</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>17801.64</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2503</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Padaria Central</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Cardápio laminado</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>4.243,09</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2504</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>23-jul-26</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Em pré-impressão</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>11521.21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2505</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Bebidas Jangada</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>18.000</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>09-jul-26</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>8674.01</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2506</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>28.004,11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2507</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Bebidas Jangada</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Embalagem flexível</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>05-jul-26</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Flexo 1</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>21262.83</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2508</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>05-jul-26</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>33157.75</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2509</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>6.000</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>27.604,40</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2510</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Rede Sabor Caseiro</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>05-jul-26</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>16958.71</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2511</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>04-jul-26</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>39795.59</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2512</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>33.257,98</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2513</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Calendário de mesa</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>19-jul-26</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>27622.18</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2514</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Distrib. Sertão</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>14-jul-26</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>41088.83</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2515</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Rótulo adesivo</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>17.631,52</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2516</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Farmácia Bem Estar</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>31-jul-26</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>EM PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>15766.68</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2517</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Padaria Central</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cardápio laminado</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>11.000</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>16-jul-26</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Em pré-impressão</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>37286.55</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2518</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Caixa cartucho</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>Aguardando aprovação</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>25.571,33</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2519</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Farmácia Bem Estar</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>27-jul-26</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>Offset 2</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8.700,00</t>
+      <c r="I109" t="n">
+        <v>32123.31</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2520</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Supermercados Praia Nova</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Folder 3 dobras</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>29-jun-26</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>9319.43</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2521</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Frigorífico Boi Dourado</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Embalagem flexível</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>35.000</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>36.737,29</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2522</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Padaria Central</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Catálogo institucional</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>03-ago-26</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Aguardando papel</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>41383.28</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2523</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>01-jul-26</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Offset 3</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>26705.18</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2524</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Cosméticos Flor de Lis</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>em produção</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>10.201,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2525</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cardápio laminado</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>25.000</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>12-jul-26</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>29109.53</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2526</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Distribuidora Sertão</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>08-jul-26</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Aguardando aprovação</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>9591.08</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2527</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Cartaz A2</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>17.148,37</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2528</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Confecções Tropical</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Catálogo institucional</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>01-ago-26</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>37942.43</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2529</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sacola personalizada</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>05-jul-26</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Flexo 2</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>17162.75</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2530</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Laticínios Vale Verde</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Offset 1</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>20.342,99</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2531</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>06-jul-26</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Aguardando aprovação</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>15228.63</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2532</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Bebidas Jangada</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>02-jul-26</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Em produção</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>30076.37</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2533</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Cosméticos Flor de Lis</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Calendário de mesa</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Em acabamento</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>16.334,79</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2534</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Distribuidora Sertão</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Bloco de notas</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>15-jul-26</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>entregue</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Digital 1</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>4409.07</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2535</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Editora Céu Azul</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>09-jul-26</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ENTREGUE</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Offset 2</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>29966.17</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Relatório gerado automaticamente pelo módulo PCP. Não editar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Status é preenchido manualmente pelo líder de máquina no fim do turno.</t>
         </is>
       </c>
     </row>
